--- a/data/nzd0021/nzd0021.xlsx
+++ b/data/nzd0021/nzd0021.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E250"/>
+  <dimension ref="A1:E251"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5680,6 +5680,27 @@
         <v>362.46</v>
       </c>
       <c r="E250" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-10 22:17:07+00:00</t>
+        </is>
+      </c>
+      <c r="B251" t="n">
+        <v>353.39</v>
+      </c>
+      <c r="C251" t="n">
+        <v>346.02</v>
+      </c>
+      <c r="D251" t="n">
+        <v>363.77</v>
+      </c>
+      <c r="E251" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -5696,7 +5717,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B266"/>
+  <dimension ref="A1:B267"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8359,6 +8380,16 @@
       </c>
       <c r="B266" t="n">
         <v>-0.24</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>2026-07-10 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B267" t="n">
+        <v>-0.92</v>
       </c>
     </row>
   </sheetData>
@@ -8527,28 +8558,28 @@
         <v>0.06710000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.3572559953605054</v>
+        <v>-0.364517732239076</v>
       </c>
       <c r="J2" t="n">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="K2" t="n">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="L2" t="n">
-        <v>0.129260088353565</v>
+        <v>0.1342660912161795</v>
       </c>
       <c r="M2" t="n">
-        <v>5.78987211359448</v>
+        <v>5.802179927425849</v>
       </c>
       <c r="N2" t="n">
-        <v>53.06603981430825</v>
+        <v>53.18645234529003</v>
       </c>
       <c r="O2" t="n">
-        <v>7.284644110339794</v>
+        <v>7.292904246271854</v>
       </c>
       <c r="P2" t="n">
-        <v>372.1858457017028</v>
+        <v>372.2553078436708</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -8605,28 +8636,28 @@
         <v>0.0956</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.2467158198726962</v>
+        <v>-0.2548740434688563</v>
       </c>
       <c r="J3" t="n">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="K3" t="n">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0579214758383455</v>
+        <v>0.06174439925805209</v>
       </c>
       <c r="M3" t="n">
-        <v>6.24998140121351</v>
+        <v>6.261264277335692</v>
       </c>
       <c r="N3" t="n">
-        <v>61.10476874997984</v>
+        <v>61.28023680462978</v>
       </c>
       <c r="O3" t="n">
-        <v>7.816953930398966</v>
+        <v>7.828169441486929</v>
       </c>
       <c r="P3" t="n">
-        <v>362.9703414839311</v>
+        <v>363.0483789693316</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -8683,28 +8714,28 @@
         <v>0.075</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.03562940755608131</v>
+        <v>-0.03943094373534362</v>
       </c>
       <c r="J4" t="n">
+        <v>250</v>
+      </c>
+      <c r="K4" t="n">
         <v>249</v>
       </c>
-      <c r="K4" t="n">
-        <v>248</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.002489974649132365</v>
+        <v>0.003069106570532831</v>
       </c>
       <c r="M4" t="n">
-        <v>4.318748511788064</v>
+        <v>4.319124672984406</v>
       </c>
       <c r="N4" t="n">
-        <v>31.07791649808957</v>
+        <v>31.0429809143805</v>
       </c>
       <c r="O4" t="n">
-        <v>5.574757079738055</v>
+        <v>5.571622825926078</v>
       </c>
       <c r="P4" t="n">
-        <v>369.4918469864751</v>
+        <v>369.5285321681733</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -8746,7 +8777,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E250"/>
+  <dimension ref="A1:E251"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15495,6 +15526,33 @@
         </is>
       </c>
     </row>
+    <row r="251">
+      <c r="A251" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-10 22:17:07+00:00</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>-34.80758321764599,173.16370485569314</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>-34.808308067412895,173.1635162137594</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>-34.80905943849854,173.1636072877952</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0021/nzd0021.xlsx
+++ b/data/nzd0021/nzd0021.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E251"/>
+  <dimension ref="A1:E252"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5703,6 +5703,27 @@
       <c r="E251" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-19 22:17:20+00:00</t>
+        </is>
+      </c>
+      <c r="B252" t="n">
+        <v>355.28</v>
+      </c>
+      <c r="C252" t="n">
+        <v>346.97</v>
+      </c>
+      <c r="D252" t="n">
+        <v>364.39</v>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -5717,7 +5738,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B267"/>
+  <dimension ref="A1:B268"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8390,6 +8411,16 @@
       </c>
       <c r="B267" t="n">
         <v>-0.92</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>2026-08-19 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B268" t="n">
+        <v>0.03</v>
       </c>
     </row>
   </sheetData>
@@ -8558,28 +8589,28 @@
         <v>0.06710000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.364517732239076</v>
+        <v>-0.3701293752493056</v>
       </c>
       <c r="J2" t="n">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="K2" t="n">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1342660912161795</v>
+        <v>0.1385754732523945</v>
       </c>
       <c r="M2" t="n">
-        <v>5.802179927425849</v>
+        <v>5.806382495948665</v>
       </c>
       <c r="N2" t="n">
-        <v>53.18645234529003</v>
+        <v>53.17437970140569</v>
       </c>
       <c r="O2" t="n">
-        <v>7.292904246271854</v>
+        <v>7.292076501340732</v>
       </c>
       <c r="P2" t="n">
-        <v>372.2553078436708</v>
+        <v>372.3092370577399</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -8636,28 +8667,28 @@
         <v>0.0956</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.2548740434688563</v>
+        <v>-0.262107380215254</v>
       </c>
       <c r="J3" t="n">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="K3" t="n">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="L3" t="n">
-        <v>0.06174439925805209</v>
+        <v>0.06533364537768671</v>
       </c>
       <c r="M3" t="n">
-        <v>6.261264277335692</v>
+        <v>6.268050893530263</v>
       </c>
       <c r="N3" t="n">
-        <v>61.28023680462978</v>
+        <v>61.36810029375659</v>
       </c>
       <c r="O3" t="n">
-        <v>7.828169441486929</v>
+        <v>7.83377943867177</v>
       </c>
       <c r="P3" t="n">
-        <v>363.0483789693316</v>
+        <v>363.1178930430386</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -8714,28 +8745,28 @@
         <v>0.075</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.03943094373534362</v>
+        <v>-0.04266332820848513</v>
       </c>
       <c r="J4" t="n">
+        <v>251</v>
+      </c>
+      <c r="K4" t="n">
         <v>250</v>
       </c>
-      <c r="K4" t="n">
-        <v>249</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.003069106570532831</v>
+        <v>0.003618776249273203</v>
       </c>
       <c r="M4" t="n">
-        <v>4.319124672984406</v>
+        <v>4.31676351002517</v>
       </c>
       <c r="N4" t="n">
-        <v>31.0429809143805</v>
+        <v>30.98416797457768</v>
       </c>
       <c r="O4" t="n">
-        <v>5.571622825926078</v>
+        <v>5.566342423403152</v>
       </c>
       <c r="P4" t="n">
-        <v>369.5285321681733</v>
+        <v>369.5598695336903</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -8777,7 +8808,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E251"/>
+  <dimension ref="A1:E252"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15553,6 +15584,33 @@
         </is>
       </c>
     </row>
+    <row r="252">
+      <c r="A252" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-19 22:17:20+00:00</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>-34.80758525622215,173.1637253709878</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>-34.80830905941936,173.1635265304658</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>-34.80906006456344,173.16361402383194</t>
+        </is>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0021/nzd0021.xlsx
+++ b/data/nzd0021/nzd0021.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E252"/>
+  <dimension ref="A1:E253"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5724,6 +5724,27 @@
       <c r="E252" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-28 22:17:40+00:00</t>
+        </is>
+      </c>
+      <c r="B253" t="n">
+        <v>358.79</v>
+      </c>
+      <c r="C253" t="n">
+        <v>348.78</v>
+      </c>
+      <c r="D253" t="n">
+        <v>364.89</v>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -5738,7 +5759,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B268"/>
+  <dimension ref="A1:B269"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8421,6 +8442,16 @@
       </c>
       <c r="B268" t="n">
         <v>0.03</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>2026-09-28 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B269" t="n">
+        <v>0.8100000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -8589,28 +8620,28 @@
         <v>0.06710000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.3701293752493056</v>
+        <v>-0.3728589541066027</v>
       </c>
       <c r="J2" t="n">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="K2" t="n">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1385754732523945</v>
+        <v>0.1414153987374341</v>
       </c>
       <c r="M2" t="n">
-        <v>5.806382495948665</v>
+        <v>5.79646289994594</v>
       </c>
       <c r="N2" t="n">
-        <v>53.17437970140569</v>
+        <v>53.01092808770139</v>
       </c>
       <c r="O2" t="n">
-        <v>7.292076501340732</v>
+        <v>7.280860394740541</v>
       </c>
       <c r="P2" t="n">
-        <v>372.3092370577399</v>
+        <v>372.3355905861659</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -8667,28 +8698,28 @@
         <v>0.0956</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.262107380215254</v>
+        <v>-0.267767192478376</v>
       </c>
       <c r="J3" t="n">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="K3" t="n">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="L3" t="n">
-        <v>0.06533364537768671</v>
+        <v>0.06840172288263868</v>
       </c>
       <c r="M3" t="n">
-        <v>6.268050893530263</v>
+        <v>6.267770379515031</v>
       </c>
       <c r="N3" t="n">
-        <v>61.36810029375659</v>
+        <v>61.32904852956385</v>
       </c>
       <c r="O3" t="n">
-        <v>7.83377943867177</v>
+        <v>7.831286518163146</v>
       </c>
       <c r="P3" t="n">
-        <v>363.1178930430386</v>
+        <v>363.1725373787254</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -8745,28 +8776,28 @@
         <v>0.075</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.04266332820848513</v>
+        <v>-0.0454382577060525</v>
       </c>
       <c r="J4" t="n">
+        <v>252</v>
+      </c>
+      <c r="K4" t="n">
         <v>251</v>
       </c>
-      <c r="K4" t="n">
-        <v>250</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.003618776249273203</v>
+        <v>0.004136750971197478</v>
       </c>
       <c r="M4" t="n">
-        <v>4.31676351002517</v>
+        <v>4.312453008375721</v>
       </c>
       <c r="N4" t="n">
-        <v>30.98416797457768</v>
+        <v>30.90917919584436</v>
       </c>
       <c r="O4" t="n">
-        <v>5.566342423403152</v>
+        <v>5.559602431455361</v>
       </c>
       <c r="P4" t="n">
-        <v>369.5598695336903</v>
+        <v>369.5868955613093</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -8808,7 +8839,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E252"/>
+  <dimension ref="A1:E253"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15611,6 +15642,33 @@
         </is>
       </c>
     </row>
+    <row r="253">
+      <c r="A253" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-28 22:17:40+00:00</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>-34.80758904214009,173.1637634708234</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>-34.80831094945032,173.16354618650706</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>-34.80906056945424,173.1636194561197</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
